--- a/entertainment_forms/025_party_bus_waiver_form--entertainment_forms.xlsx
+++ b/entertainment_forms/025_party_bus_waiver_form--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -859,7 +859,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Emergency Phone</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Contact E-mail</t>
+          <t>Emergency Contact Email</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -997,7 +997,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Emergency Contact Phone</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>emergency_contact_email</t>
+          <t>emergency_contact_email_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Contact E-mail</t>
+          <t>Emergency Contact Email 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Emergency Contact Employer Address</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Emergency Contact Employer Phone</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Contact E-mail</t>
+          <t>Emergency Contact Employer Email</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1211,29 +1211,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bus_capacity_choices</t>
+          <t>bus_equipment_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>stereo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>Stereo</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>stereo</t>
+          <t>dvd_player</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stereo</t>
+          <t>DVD Player</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dvd_player</t>
+          <t>dance_floor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DVD Player</t>
+          <t>Dance Floor</t>
         </is>
       </c>
     </row>
@@ -1279,27 +1279,10 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dance_floor</t>
+          <t>restroom</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
-        <is>
-          <t>Dance Floor</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>bus_equipment_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>restroom</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
         <is>
           <t>Restroom</t>
         </is>
